--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487161_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487161_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2828</v>
+        <v>8.4236</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0639</v>
+        <v>5.9637</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2189</v>
+        <v>2.4598</v>
       </c>
       <c r="G2" t="n">
         <v>7.5141</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1897</v>
+        <v>0.3305</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4297</v>
+        <v>0.3295</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2399</v>
+        <v>0.001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8105</v>
+        <v>8.1645</v>
       </c>
       <c r="E3" t="n">
-        <v>7.521</v>
+        <v>7.8214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2895</v>
+        <v>0.3431</v>
       </c>
       <c r="G3" t="n">
         <v>5.9218</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2208</v>
+        <v>0.5212</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1547</v>
+        <v>-0.1012</v>
       </c>
       <c r="V3" t="n">
         <v>0.8576</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2752</v>
+        <v>7.4625</v>
       </c>
       <c r="E4" t="n">
         <v>8.4323</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1572</v>
+        <v>-0.9698</v>
       </c>
       <c r="G4" t="n">
         <v>10.7163</v>
@@ -766,13 +766,13 @@
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.273</v>
+        <v>0.4604</v>
       </c>
       <c r="T4" t="n">
         <v>0.4587</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1858</v>
+        <v>0.0016</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1701</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1154</v>
+        <v>4.7619</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9841</v>
+        <v>2.7918</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1313</v>
+        <v>1.9701</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5605</v>
+        <v>2.8953</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0839</v>
+        <v>-0.4242</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6444</v>
+        <v>3.3195</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0015</v>
+        <v>1.9741</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3107</v>
+        <v>-0.1501</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3092</v>
+        <v>2.1242</v>
       </c>
       <c r="M5" t="n">
-        <v>1.562</v>
+        <v>0.9212</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2268</v>
+        <v>-0.2741</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3352</v>
+        <v>1.1953</v>
       </c>
       <c r="P5" t="n">
-        <v>0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8179</v>
+        <v>0.1755</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9507</v>
+        <v>0.2918</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8672</v>
+        <v>-0.1164</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.228</v>
+        <v>1.8842</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0471</v>
+        <v>3.5037</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2911</v>
+        <v>2.7147</v>
       </c>
       <c r="F6" t="n">
-        <v>1.756</v>
+        <v>0.789</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8953</v>
+        <v>3.849</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4242</v>
+        <v>1.2429</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3195</v>
+        <v>2.6062</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9741</v>
+        <v>3.1815</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1501</v>
+        <v>1.9041</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1242</v>
+        <v>1.2774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9212</v>
+        <v>0.6675</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2741</v>
+        <v>-0.6612</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1953</v>
+        <v>1.3288</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R6" t="n">
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5394</v>
+        <v>1.0986</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2089</v>
+        <v>1.2004</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3305</v>
+        <v>-0.1018</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8842</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5717</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7502</v>
+        <v>3.1979</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8541</v>
+        <v>0.4414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.896</v>
+        <v>2.7565</v>
       </c>
       <c r="G7" t="n">
-        <v>3.849</v>
+        <v>1.5605</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2429</v>
+        <v>-0.0839</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6062</v>
+        <v>1.6444</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1815</v>
+        <v>-0.0015</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9041</v>
+        <v>-0.3107</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2774</v>
+        <v>0.3092</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6675</v>
+        <v>1.562</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6612</v>
+        <v>0.2268</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3288</v>
+        <v>1.3352</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.158</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.345</v>
+        <v>1.9003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3398</v>
+        <v>1.4079</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0053</v>
+        <v>0.4924</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.042</v>
+        <v>2.3414</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1647</v>
+        <v>0.2953</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2067</v>
+        <v>2.0461</v>
       </c>
       <c r="G8" t="n">
         <v>2.4482</v>
@@ -1078,13 +1078,13 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4587</v>
+        <v>0.7581</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1917</v>
+        <v>0.6518</v>
       </c>
       <c r="U8" t="n">
-        <v>0.267</v>
+        <v>0.1064</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2601</v>
+        <v>1.6805</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.1298</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8906</v>
+        <v>1.8103</v>
       </c>
       <c r="G9" t="n">
         <v>2.2919</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0668</v>
+        <v>0.3536</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>0.2628</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1712</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2735</v>
+        <v>0.1326</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3432</v>
+        <v>-0.4996</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0697</v>
+        <v>0.6322</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3785</v>
+        <v>0.0732</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5784</v>
+        <v>0.4037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1999</v>
+        <v>-0.3306</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.512</v>
+        <v>-1.0282</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5848</v>
+        <v>0.1035</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0728</v>
+        <v>-1.1317</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1335</v>
+        <v>1.1014</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0064</v>
+        <v>0.3002</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1271</v>
+        <v>0.8011</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7099</v>
+        <v>0.0595</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.2657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2684</v>
+        <v>-0.2062</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.842</v>
+        <v>1.228</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0767</v>
+        <v>-0.3204</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6734</v>
+        <v>0.6422</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7501</v>
+        <v>-0.9627</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4259</v>
+        <v>-0.3785</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9186</v>
+        <v>-0.5784</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4926</v>
+        <v>0.1999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9133</v>
+        <v>-0.512</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4841</v>
+        <v>-0.5848</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5709</v>
+        <v>0.0728</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4873</v>
+        <v>0.1335</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4345</v>
+        <v>0.0064</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9218</v>
+        <v>0.1271</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3326</v>
+        <v>0.116</v>
       </c>
       <c r="T11" t="n">
-        <v>2.135</v>
+        <v>0.2773</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1976</v>
+        <v>-0.1613</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0492</v>
+        <v>-1.1666</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3602</v>
+        <v>-2.5151</v>
       </c>
       <c r="F12" t="n">
-        <v>0.311</v>
+        <v>1.3485</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0732</v>
+        <v>-0.4259</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4037</v>
+        <v>-2.9186</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3306</v>
+        <v>2.4926</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0282</v>
+        <v>-0.9133</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1035</v>
+        <v>-2.4841</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1317</v>
+        <v>1.5709</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1014</v>
+        <v>0.4873</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3002</v>
+        <v>-0.4345</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8011</v>
+        <v>0.9218</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1224</v>
+        <v>1.0893</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5949</v>
+        <v>1.2932</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5275</v>
+        <v>-0.204</v>
       </c>
       <c r="V12" t="n">
+        <v>-0.2859</v>
+      </c>
+      <c r="W12" t="n">
         <v>0</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.228</v>
-      </c>
       <c r="X12" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>37.8843</v>
+        <v>38.1816</v>
       </c>
       <c r="E13" t="n">
-        <v>25.6609</v>
+        <v>25.9583</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2232</v>
+        <v>12.2231</v>
       </c>
       <c r="G13" t="n">
         <v>36.4659</v>
       </c>
       <c r="H13" t="n">
-        <v>5.273700000000001</v>
+        <v>5.273700000000002</v>
       </c>
       <c r="I13" t="n">
         <v>31.1919</v>
@@ -1447,10 +1447,10 @@
         <v>6.912700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>21.91000000000001</v>
+        <v>21.91</v>
       </c>
       <c r="M13" t="n">
-        <v>7.6433</v>
+        <v>7.643299999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-1.6389</v>
@@ -1468,13 +1468,13 @@
         <v>14.4757</v>
       </c>
       <c r="S13" t="n">
-        <v>6.464299999999999</v>
+        <v>6.761799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>6.6629</v>
+        <v>6.9603</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1985</v>
+        <v>-0.1986</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1859</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1948</v>
+        <v>0.8471</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4469</v>
+        <v>1.0463</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2521</v>
+        <v>-0.1992</v>
       </c>
       <c r="G14" t="n">
         <v>0.6269</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3199</v>
+        <v>-0.6676</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4429</v>
+        <v>0.0423</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7628</v>
+        <v>-0.7099</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6562</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0916</v>
+        <v>-1.4186</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8129</v>
+        <v>-1.9187</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7213</v>
+        <v>0.5001</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8858</v>
+        <v>-1.7904</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8082</v>
+        <v>-0.2959</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.694</v>
+        <v>-1.4944</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5917</v>
+        <v>-1.8579</v>
       </c>
       <c r="K15" t="n">
-        <v>2.551</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0407</v>
+        <v>-1.3352</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.4775</v>
+        <v>0.0675</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7428</v>
+        <v>0.2268</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7347</v>
+        <v>-0.1592</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4286</v>
+        <v>-0.7863</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9885</v>
+        <v>-0.0608</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5599</v>
+        <v>-0.7255</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0776</v>
+        <v>-1.5158</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5809</v>
+        <v>-1.5439</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6585</v>
+        <v>0.0281</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.918</v>
+        <v>-1.8945</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8234</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.0946</v>
+        <v>-2.649</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2469</v>
+        <v>-0.9272</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2876</v>
+        <v>1.035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>-1.9621</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.6711</v>
+        <v>-0.9674</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5358</v>
+        <v>-0.2805</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.1353</v>
+        <v>-0.6869</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9301</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5123</v>
+        <v>0.0929</v>
       </c>
       <c r="T16" t="n">
-        <v>0.279</v>
+        <v>0.0625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2333</v>
+        <v>0.0304</v>
       </c>
       <c r="V16" t="n">
-        <v>3.398</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7418</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.602</v>
+        <v>-1.5654</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8443</v>
+        <v>0.2805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2422</v>
+        <v>-1.8459</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8945</v>
+        <v>-6.918</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7544999999999999</v>
+        <v>-3.8234</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.649</v>
+        <v>-3.0946</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9272</v>
+        <v>-2.2469</v>
       </c>
       <c r="K17" t="n">
-        <v>1.035</v>
+        <v>-2.2876</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9621</v>
+        <v>0.0407</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9674</v>
+        <v>-4.6711</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2805</v>
+        <v>-1.5358</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6869</v>
+        <v>-3.1353</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>1.9301</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0066</v>
+        <v>0.0245</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.238</v>
+        <v>-0.0214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2446</v>
+        <v>0.0459</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2859</v>
+        <v>3.398</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0594</v>
+        <v>-2.4853</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3193</v>
+        <v>0.2092</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2599</v>
+        <v>-2.6945</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7904</v>
+        <v>-1.8858</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2959</v>
+        <v>0.8082</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4944</v>
+        <v>-2.694</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8579</v>
+        <v>2.5917</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5227000000000001</v>
+        <v>2.551</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3352</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0675</v>
+        <v>-4.4775</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2268</v>
+        <v>-1.7428</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1592</v>
+        <v>-2.7347</v>
       </c>
       <c r="P18" t="n">
-        <v>1.158</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4271</v>
+        <v>0.8517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4614</v>
+        <v>1.3848</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9657</v>
+        <v>-0.5331</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.648</v>
+        <v>-3.5479</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2279</v>
+        <v>-1.1277</v>
       </c>
       <c r="F19" t="n">
         <v>-2.4202</v>
@@ -1936,10 +1936,10 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1144</v>
+        <v>-1.0143</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.4075</v>
       </c>
       <c r="U19" t="n">
         <v>-0.6068</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9157</v>
+        <v>-4.3401</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0825</v>
+        <v>-0.2233</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8332</v>
+        <v>-4.1168</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9901</v>
+        <v>-2.4935</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8495</v>
+        <v>1.0816</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1406</v>
+        <v>-3.5751</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4227</v>
+        <v>1.1159</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7958</v>
+        <v>1.8163</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6269</v>
+        <v>-0.7004</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5674</v>
+        <v>-3.6094</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0537</v>
+        <v>-0.7347</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5137</v>
+        <v>-2.8747</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3815</v>
+        <v>-1.0698</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0423</v>
+        <v>-0.3741</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4238</v>
+        <v>-0.6957</v>
       </c>
       <c r="V20" t="n">
-        <v>1.228</v>
+        <v>-2.1278</v>
       </c>
       <c r="W20" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.435</v>
+        <v>-4.4811</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0244</v>
+        <v>-3.1826</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4106</v>
+        <v>-1.2984</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4935</v>
+        <v>-3.9901</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0816</v>
+        <v>-1.8495</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5751</v>
+        <v>-2.1406</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1159</v>
+        <v>-2.4227</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8163</v>
+        <v>-1.7958</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7004</v>
+        <v>-0.6269</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6094</v>
+        <v>-1.5674</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7347</v>
+        <v>-0.0537</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8747</v>
+        <v>-1.5137</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3511</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3161</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1647</v>
+        <v>-0.9469</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1752</v>
+        <v>-0.0578</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9895</v>
+        <v>-0.889</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1278</v>
+        <v>1.228</v>
       </c>
       <c r="W21" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.1278</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3025</v>
+        <v>-6.3408</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7047</v>
+        <v>-1.9035</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5979</v>
+        <v>-4.4372</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3399</v>
@@ -2170,13 +2170,13 @@
         <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7648</v>
+        <v>-0.8031</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9967</v>
+        <v>-0.1956</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7681</v>
+        <v>-0.6075</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.1303</v>
+        <v>-11.7012</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.861</v>
+        <v>-3.8595</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.269399999999999</v>
+        <v>-7.8417</v>
       </c>
       <c r="G23" t="n">
         <v>-7.5398</v>
@@ -2248,13 +2248,13 @@
         <v>1.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2394</v>
+        <v>-0.8104</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1752</v>
+        <v>-0.1738</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0642</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.228</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-37.8841</v>
+        <v>-36.5491</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.2234</v>
+        <v>-12.2232</v>
       </c>
       <c r="F24" t="n">
-        <v>-25.6611</v>
+        <v>-24.3257</v>
       </c>
       <c r="G24" t="n">
         <v>-36.46559999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.2736</v>
+        <v>-5.273600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-31.192</v>
@@ -2317,7 +2317,7 @@
         <v>-21.9098</v>
       </c>
       <c r="P24" t="n">
-        <v>3.8602</v>
+        <v>3.860199999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.4755</v>
@@ -2326,13 +2326,13 @@
         <v>18.3357</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.4643</v>
+        <v>-5.129300000000001</v>
       </c>
       <c r="T24" t="n">
         <v>0.1986000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.6629</v>
+        <v>-5.3278</v>
       </c>
       <c r="V24" t="n">
         <v>1.1858</v>
